--- a/artfynd/A 32256-2024 artfynd.xlsx
+++ b/artfynd/A 32256-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119291801</v>
       </c>
       <c r="B2" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119291752</v>
+        <v>119300703</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gravabergsbäcken, Gravabergsbäcken, Ång</t>
+          <t>Gravabergstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568282</v>
+        <v>568343</v>
       </c>
       <c r="R3" t="n">
-        <v>7054846</v>
+        <v>7054806</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,24 +843,9 @@
           <t>2024-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,74 +854,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119300703</v>
+        <v>119291752</v>
       </c>
       <c r="B4" t="n">
-        <v>91861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gravabergstjärnen, Ång</t>
+          <t>Gravabergsbäcken, Gravabergsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568343</v>
+        <v>568282</v>
       </c>
       <c r="R4" t="n">
-        <v>7054806</v>
+        <v>7054846</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,9 +941,24 @@
           <t>2024-08-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,19 +967,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 32256-2024 artfynd.xlsx
+++ b/artfynd/A 32256-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119291801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300703</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119291752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>